--- a/InputData/trans/BRASC/BAU Rng Anxiety Shadow Costs.xlsx
+++ b/InputData/trans/BRASC/BAU Rng Anxiety Shadow Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BRASC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onewri-my.sharepoint.com/personal/khushi_parakh_wri_org/Documents/Desktop/EPS update/current WIP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB37FF9-DC7A-43A7-A458-56F2E308DCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{6EB37FF9-DC7A-43A7-A458-56F2E308DCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{652A4E09-A689-41A2-A002-47552A44A51D}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="260" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>Source:</t>
   </si>
@@ -107,21 +107,6 @@
     <t>cv (thousand USD)</t>
   </si>
   <si>
-    <t>https://www.census.gov/library/publications/2020/demo/p60-270.html</t>
-  </si>
-  <si>
-    <t>Median US Income</t>
-  </si>
-  <si>
-    <t>United States Census Bureau</t>
-  </si>
-  <si>
-    <t>Income and Poverty in the United States: 2019</t>
-  </si>
-  <si>
-    <t>First bullet of "Highlights"</t>
-  </si>
-  <si>
     <t>2019 to 2012 USD</t>
   </si>
   <si>
@@ -149,15 +134,6 @@
     <t>median range ice (hundred miles)</t>
   </si>
   <si>
-    <t>Inside Evs</t>
-  </si>
-  <si>
-    <t>The Median Range of Fully Electric Vehicles Exceeded 250 Miles in 2020</t>
-  </si>
-  <si>
-    <t>https://insideevs.com/news/464449/median-range-evs-2020-exceeded-250-miles/</t>
-  </si>
-  <si>
     <t>EV range</t>
   </si>
   <si>
@@ -167,18 +143,9 @@
     <t>The Range Compensating Value uses parameters from the DOE study, the median household income,</t>
   </si>
   <si>
-    <t>and the median ranges of ICE and EV vehicles. For EV vehicles, the current median range has already surpassed</t>
-  </si>
-  <si>
     <t>Currency Conversion</t>
   </si>
   <si>
-    <t xml:space="preserve">250 miles and is forecated to continue improving. Therefore, we start with today's median range, and assume </t>
-  </si>
-  <si>
-    <t>the range will reach 300 miles by 2050.</t>
-  </si>
-  <si>
     <t xml:space="preserve">*2020 median range taken from historical data. 2030 and 2050 are estimated, with the 2050 </t>
   </si>
   <si>
@@ -186,14 +153,88 @@
   </si>
   <si>
     <t>BRAaCTSC BAU Range Anxiety Shadow Cost</t>
+  </si>
+  <si>
+    <t>EV Range</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Curvv EV 55 kWh</t>
+  </si>
+  <si>
+    <t>Curvv.ev 45 kWh</t>
+  </si>
+  <si>
+    <t>Nexon.ev 40.5 kWh</t>
+  </si>
+  <si>
+    <t>Nexon.ev 30 kWh</t>
+  </si>
+  <si>
+    <t>Punch.ev 35 kWh</t>
+  </si>
+  <si>
+    <t>Punch.ev 25 kWh</t>
+  </si>
+  <si>
+    <t>Tiago.ev 24 kWh</t>
+  </si>
+  <si>
+    <t>Tiago.ev 19.2 kWh</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Urban+Extra Urban (P1+P2) (kms) 
+[MoRTH declaration mandate. Simulates city and highway driving]</t>
+  </si>
+  <si>
+    <t>Tata Motors EV</t>
+  </si>
+  <si>
+    <t>https://ev.tatamotors.com/articles/press-releases/driving-range-declaration.html</t>
+  </si>
+  <si>
+    <t>Driving Range Declaration</t>
+  </si>
+  <si>
+    <t>and the median ranges of ICE and EV vehicles. For EV vehicles, the current median range has nearly reached</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 miles and is forecasted to continue improving. Therefore, we start with today's median range, and assume </t>
+  </si>
+  <si>
+    <t>the range is assumed to reach ICE vehicle range by 2070.</t>
+  </si>
+  <si>
+    <t>Median Indian Income</t>
+  </si>
+  <si>
+    <t>2022 INR to USD</t>
+  </si>
+  <si>
+    <t>Statista</t>
+  </si>
+  <si>
+    <t>Share of households by gross annual income across India in financial year 2021</t>
+  </si>
+  <si>
+    <t>https://www.statista.com/statistics/482584/india-households-by-annual-income/</t>
+  </si>
+  <si>
+    <t>Bar chart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -263,7 +304,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -277,7 +318,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -295,6 +344,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,186 +613,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="14">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="7">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="7">
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" s="7">
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B24" s="7">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B26" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39">
         <v>0.89805481563188172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40">
+        <v>82.79</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{14EF0A86-0973-41E2-9D23-51C96C77958E}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{33E3AFFC-E626-4354-8ABB-3CDDD82E740D}"/>
+    <hyperlink ref="B13" r:id="rId3" xr:uid="{4CB7E8C3-90CA-4BCE-A80D-4A8B8275F0F9}"/>
+    <hyperlink ref="B19" r:id="rId4" xr:uid="{85F915E1-5619-4B49-887D-CF1B242C4E48}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -747,49 +811,86 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.54296875" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
+    <col min="3" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
         <v>-0.36099999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
         <v>1.268</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
         <v>-0.11600000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>2020</v>
       </c>
@@ -799,10 +900,19 @@
       <c r="D7">
         <v>2050</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>2070</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>4.12</v>
@@ -814,61 +924,104 @@
         <f>B8</f>
         <v>4.12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>4.12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>2.59</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="B9" s="5">
+        <f>I11/1.609/100</f>
+        <v>1.9888129272840274</v>
+      </c>
+      <c r="C9" s="12">
+        <f>3*1.99/2.59</f>
+        <v>2.3050193050193051</v>
+      </c>
+      <c r="D9" s="12">
+        <f>4.12*1.99/2.59</f>
+        <v>3.1655598455598457</v>
+      </c>
+      <c r="E9">
         <v>4.12</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10">
-        <v>68.703000000000003</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="10">
+        <f>((125+500)/52*35)/About!B40</f>
+        <v>5.0812063887314523</v>
+      </c>
+      <c r="C10" s="11">
         <f>income</f>
-        <v>68.703000000000003</v>
-      </c>
-      <c r="D10" s="9">
+        <v>5.0812063887314523</v>
+      </c>
+      <c r="D10" s="11">
         <f>B10</f>
-        <v>68.703000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5.0812063887314523</v>
+      </c>
+      <c r="E10" s="10">
+        <f>income</f>
+        <v>5.0812063887314523</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11">
+        <f>MEDIAN(I3:I10)</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="5">
-        <f>($B$4/$B$2*B9*(1-B8/B9)+$B$5/$B$2*B9^2*(1-B8^2/B9^2))*LN(income)*About!$B$38</f>
-        <v>7.8828464065137096</v>
+        <f>($B$4/$B$2*B9*(1-B8/B9)+$B$5/$B$2*B9^2*(1-B8^2/B9^2))*LN(income)*About!$B$39</f>
+        <v>4.8208359693710001</v>
       </c>
       <c r="C14" s="5">
-        <f>($B$4/$B$2*C9*(1-C8/C9)+$B$5/$B$2*C9^2*(1-C8^2/C9^2))*LN(income)*About!$B$38</f>
-        <v>5.2099509525186276</v>
+        <f>($B$4/$B$2*C9*(1-C8/C9)+$B$5/$B$2*C9^2*(1-C8^2/C9^2))*LN(income)*About!$B$39</f>
+        <v>3.8363505272225358</v>
       </c>
       <c r="D14" s="5">
-        <f>($B$4/$B$2*D9*(1-D8/D9)+$B$5/$B$2*D9^2*(1-D8^2/D9^2))*LN(income)*About!$B$38</f>
+        <f>($B$4/$B$2*D9*(1-D8/D9)+$B$5/$B$2*D9^2*(1-D8^2/D9^2))*LN(income)*About!$B$39</f>
+        <v>1.6321362284397252</v>
+      </c>
+      <c r="E14" s="5">
+        <f>($B$4/$B$2*E9*(1-E8/E9)+$B$5/$B$2*E9^2*(1-E8^2/E9^2))*LN(income)*About!$B$39</f>
         <v>0</v>
       </c>
     </row>
@@ -883,13 +1036,13 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -986,138 +1139,465 @@
       <c r="AF1" s="4">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="4">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="4">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="4">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="4">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="4">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="4">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="4">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="4">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="4">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="4">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" cm="1">
-        <f t="array" ref="B2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,B1)*1000*About!$B$38</f>
-        <v>7079.2281762560442</v>
+        <f t="array" ref="B2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,B1)*1000*About!$B$39</f>
+        <v>4329.374957665008</v>
       </c>
       <c r="C2" s="3" cm="1">
-        <f t="array" ref="C2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,C1)*1000*About!$B$38</f>
-        <v>6839.1875128420379</v>
+        <f t="array" ref="C2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,C1)*1000*About!$B$39</f>
+        <v>4240.9627684409161</v>
       </c>
       <c r="D2" s="3" cm="1">
-        <f t="array" ref="D2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,D1)*1000*About!$B$38</f>
-        <v>6599.1468494279288</v>
+        <f t="array" ref="D2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,D1)*1000*About!$B$39</f>
+        <v>4152.5505792168251</v>
       </c>
       <c r="E2" s="3" cm="1">
-        <f t="array" ref="E2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,E1)*1000*About!$B$38</f>
-        <v>6359.1061860138198</v>
+        <f t="array" ref="E2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,E1)*1000*About!$B$39</f>
+        <v>4064.1383899927332</v>
       </c>
       <c r="F2" s="3" cm="1">
-        <f t="array" ref="F2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,F1)*1000*About!$B$38</f>
-        <v>6119.0655225997107</v>
+        <f t="array" ref="F2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,F1)*1000*About!$B$39</f>
+        <v>3975.7262007686418</v>
       </c>
       <c r="G2" s="3" cm="1">
-        <f t="array" ref="G2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,G1)*1000*About!$B$38</f>
-        <v>5879.0248591857035</v>
+        <f t="array" ref="G2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,G1)*1000*About!$B$39</f>
+        <v>3887.3140115445508</v>
       </c>
       <c r="H2" s="3" cm="1">
-        <f t="array" ref="H2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,H1)*1000*About!$B$38</f>
-        <v>5638.9841957715944</v>
+        <f t="array" ref="H2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,H1)*1000*About!$B$39</f>
+        <v>3798.9018223204594</v>
       </c>
       <c r="I2" s="3" cm="1">
-        <f t="array" ref="I2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,I1)*1000*About!$B$38</f>
-        <v>5398.9435323574853</v>
+        <f t="array" ref="I2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,I1)*1000*About!$B$39</f>
+        <v>3710.4896330963675</v>
       </c>
       <c r="J2" s="3" cm="1">
-        <f t="array" ref="J2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,J1)*1000*About!$B$38</f>
-        <v>5158.9028689433762</v>
+        <f t="array" ref="J2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,J1)*1000*About!$B$39</f>
+        <v>3622.0774438722765</v>
       </c>
       <c r="K2" s="3" cm="1">
-        <f t="array" ref="K2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,K1)*1000*About!$B$38</f>
-        <v>4918.8622055292672</v>
+        <f t="array" ref="K2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,K1)*1000*About!$B$39</f>
+        <v>3533.6652546481851</v>
       </c>
       <c r="L2" s="3" cm="1">
-        <f t="array" ref="L2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,L1)*1000*About!$B$38</f>
-        <v>4678.8215421152599</v>
+        <f t="array" ref="L2">TREND(Calculations!$B$14:$C$14,Calculations!$B$7:$C$7,L1)*1000*About!$B$39</f>
+        <v>3445.2530654240936</v>
       </c>
       <c r="M2" s="3" cm="1">
-        <f t="array" ref="M2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,M1)*1000*About!$B$38</f>
-        <v>4444.8804650095735</v>
+        <f t="array" ref="M2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,M1)*1000*About!$B$39</f>
+        <v>3346.277802138789</v>
       </c>
       <c r="N2" s="3" cm="1">
-        <f t="array" ref="N2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,N1)*1000*About!$B$38</f>
-        <v>4210.9393879037852</v>
+        <f t="array" ref="N2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,N1)*1000*About!$B$39</f>
+        <v>3247.3025388534593</v>
       </c>
       <c r="O2" s="3" cm="1">
-        <f t="array" ref="O2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,O1)*1000*About!$B$38</f>
-        <v>3976.998310797997</v>
+        <f t="array" ref="O2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,O1)*1000*About!$B$39</f>
+        <v>3148.3272755681292</v>
       </c>
       <c r="P2" s="3" cm="1">
-        <f t="array" ref="P2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,P1)*1000*About!$B$38</f>
-        <v>3743.0572336923101</v>
+        <f t="array" ref="P2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,P1)*1000*About!$B$39</f>
+        <v>3049.3520122827995</v>
       </c>
       <c r="Q2" s="3" cm="1">
-        <f t="array" ref="Q2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Q1)*1000*About!$B$38</f>
-        <v>3509.1161565865218</v>
+        <f t="array" ref="Q2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Q1)*1000*About!$B$39</f>
+        <v>2950.3767489974698</v>
       </c>
       <c r="R2" s="3" cm="1">
-        <f t="array" ref="R2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,R1)*1000*About!$B$38</f>
-        <v>3275.1750794807331</v>
+        <f t="array" ref="R2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,R1)*1000*About!$B$39</f>
+        <v>2851.4014857121401</v>
       </c>
       <c r="S2" s="3" cm="1">
-        <f t="array" ref="S2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,S1)*1000*About!$B$38</f>
-        <v>3041.2340023749448</v>
+        <f t="array" ref="S2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,S1)*1000*About!$B$39</f>
+        <v>2752.42622242681</v>
       </c>
       <c r="T2" s="3" cm="1">
-        <f t="array" ref="T2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,T1)*1000*About!$B$38</f>
-        <v>2807.2929252692584</v>
+        <f t="array" ref="T2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,T1)*1000*About!$B$39</f>
+        <v>2653.4509591414799</v>
       </c>
       <c r="U2" s="3" cm="1">
-        <f t="array" ref="U2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,U1)*1000*About!$B$38</f>
-        <v>2573.3518481634696</v>
+        <f t="array" ref="U2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,U1)*1000*About!$B$39</f>
+        <v>2554.4756958561502</v>
       </c>
       <c r="V2" s="3" cm="1">
-        <f t="array" ref="V2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,V1)*1000*About!$B$38</f>
-        <v>2339.4107710576814</v>
+        <f t="array" ref="V2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,V1)*1000*About!$B$39</f>
+        <v>2455.5004325708205</v>
       </c>
       <c r="W2" s="3" cm="1">
-        <f t="array" ref="W2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,W1)*1000*About!$B$38</f>
-        <v>2105.4696939518926</v>
+        <f t="array" ref="W2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,W1)*1000*About!$B$39</f>
+        <v>2356.5251692854904</v>
       </c>
       <c r="X2" s="3" cm="1">
-        <f t="array" ref="X2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,X1)*1000*About!$B$38</f>
-        <v>1871.5286168462062</v>
+        <f t="array" ref="X2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,X1)*1000*About!$B$39</f>
+        <v>2257.5499060001603</v>
       </c>
       <c r="Y2" s="3" cm="1">
-        <f t="array" ref="Y2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Y1)*1000*About!$B$38</f>
-        <v>1637.5875397404177</v>
+        <f t="array" ref="Y2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Y1)*1000*About!$B$39</f>
+        <v>2158.5746427148565</v>
       </c>
       <c r="Z2" s="3" cm="1">
-        <f t="array" ref="Z2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Z1)*1000*About!$B$38</f>
-        <v>1403.6464626346292</v>
+        <f t="array" ref="Z2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,Z1)*1000*About!$B$39</f>
+        <v>2059.5993794295264</v>
       </c>
       <c r="AA2" s="3" cm="1">
-        <f t="array" ref="AA2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AA1)*1000*About!$B$38</f>
-        <v>1169.7053855288407</v>
+        <f t="array" ref="AA2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AA1)*1000*About!$B$39</f>
+        <v>1960.6241161441963</v>
       </c>
       <c r="AB2" s="3" cm="1">
-        <f t="array" ref="AB2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AB1)*1000*About!$B$38</f>
-        <v>935.76430842315415</v>
+        <f t="array" ref="AB2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AB1)*1000*About!$B$39</f>
+        <v>1861.6488528588666</v>
       </c>
       <c r="AC2" s="3" cm="1">
-        <f t="array" ref="AC2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AC1)*1000*About!$B$38</f>
-        <v>701.82323131736564</v>
+        <f t="array" ref="AC2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AC1)*1000*About!$B$39</f>
+        <v>1762.6735895735367</v>
       </c>
       <c r="AD2" s="3" cm="1">
-        <f t="array" ref="AD2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AD1)*1000*About!$B$38</f>
-        <v>467.88215421157707</v>
+        <f t="array" ref="AD2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AD1)*1000*About!$B$39</f>
+        <v>1663.698326288207</v>
       </c>
       <c r="AE2" s="3" cm="1">
-        <f t="array" ref="AE2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AE1)*1000*About!$B$38</f>
-        <v>233.94107710578854</v>
+        <f t="array" ref="AE2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AE1)*1000*About!$B$39</f>
+        <v>1564.7230630028771</v>
       </c>
       <c r="AF2" s="3" cm="1">
-        <f t="array" ref="AF2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AF1)*1000*About!$B$38</f>
+        <f t="array" ref="AF2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AF1)*1000*About!$B$39</f>
+        <v>1465.7477997175472</v>
+      </c>
+      <c r="AG2" s="3" cm="1">
+        <f t="array" ref="AG2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AG1)*1000*About!$B$39</f>
+        <v>1366.7725364322173</v>
+      </c>
+      <c r="AH2" s="3" cm="1">
+        <f t="array" ref="AH2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AH1)*1000*About!$B$39</f>
+        <v>1267.7972731468874</v>
+      </c>
+      <c r="AI2" s="3" cm="1">
+        <f t="array" ref="AI2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AI1)*1000*About!$B$39</f>
+        <v>1168.8220098615575</v>
+      </c>
+      <c r="AJ2" s="3" cm="1">
+        <f t="array" ref="AJ2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AJ1)*1000*About!$B$39</f>
+        <v>1069.8467465762533</v>
+      </c>
+      <c r="AK2" s="3" cm="1">
+        <f t="array" ref="AK2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AK1)*1000*About!$B$39</f>
+        <v>970.87148329092338</v>
+      </c>
+      <c r="AL2" s="3" cm="1">
+        <f t="array" ref="AL2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AL1)*1000*About!$B$39</f>
+        <v>871.89622000559348</v>
+      </c>
+      <c r="AM2" s="3" cm="1">
+        <f t="array" ref="AM2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AM1)*1000*About!$B$39</f>
+        <v>772.92095672026369</v>
+      </c>
+      <c r="AN2" s="3" cm="1">
+        <f t="array" ref="AN2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AN1)*1000*About!$B$39</f>
+        <v>673.94569343493379</v>
+      </c>
+      <c r="AO2" s="3" cm="1">
+        <f t="array" ref="AO2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AO1)*1000*About!$B$39</f>
+        <v>574.97043014960389</v>
+      </c>
+      <c r="AP2" s="3" cm="1">
+        <f t="array" ref="AP2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AP1)*1000*About!$B$39</f>
+        <v>475.99516686427404</v>
+      </c>
+      <c r="AQ2" s="3" cm="1">
+        <f t="array" ref="AQ2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AQ1)*1000*About!$B$39</f>
+        <v>377.0199035789442</v>
+      </c>
+      <c r="AR2" s="3" cm="1">
+        <f t="array" ref="AR2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AR1)*1000*About!$B$39</f>
+        <v>278.04464029361435</v>
+      </c>
+      <c r="AS2" s="3" cm="1">
+        <f t="array" ref="AS2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AS1)*1000*About!$B$39</f>
+        <v>179.06937700828448</v>
+      </c>
+      <c r="AT2" s="3" cm="1">
+        <f t="array" ref="AT2">TREND(Calculations!$C$14:$D$14,Calculations!$C$7:$D$7,AT1)*1000*About!$B$39</f>
+        <v>80.094113722954603</v>
+      </c>
+      <c r="AU2" s="3">
         <v>0</v>
       </c>
-      <c r="AG2" s="3"/>
+      <c r="AV2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{126BF0B4-18CC-47BE-AED5-CC0FDC69C786}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB22B483-0E04-4C91-9A11-74DC1E8C8350}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C35AA13E-C51B-4922-8E34-31AAE075311B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>